--- a/recipes/onion-garlic-free-indian/focus-states/16-punjab/excel/punjab-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/16-punjab/excel/punjab-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Aloo gobhi (no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Aloo gobhi (no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Side  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -1638,31 +1641,197 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Temper. Veg. Cover-cook till tender. Dry.</t>
+          <t>Mise en place. Cut 1 cauliflower into even florets. Peel and cube 3 potatoes the same size. Set a stainless steel kadhai — never aluminium.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Rinse cauliflower in salted water 5 minutes. Drain well so it does not steam soggy.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Heat ghee. Bloom cumin and hing 20–30 seconds. Add ginger. Add potato. Toss 3 minutes.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Add cauliflower, turmeric, chilli, coriander and salt. Toss to coat. Cover. Cook on medium-low 12–15 minutes, stirring every 3 minutes, until a knife slips through potato.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Uncover. Raise heat 2–3 minutes to dry the masala so it clings, not pools. Optional chopped tomato in the last 4 minutes.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: florets tender with light brown edges, potato cooked, spice dry on the vegetable. Finish coriander.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Serve hot as a side. Hold covered 20 minutes. Do not add water at the pass or it goes mushy.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 1  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Aloo gobhi (no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="25">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1676,7 +1845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1688,7 +1857,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Baingan bharta (no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Baingan bharta (no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1698,7 +1867,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Side  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1718,44 +1887,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 10 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -1849,31 +2018,184 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Mash roasted baingan. Cook with tomato masala.</t>
+          <t>Mise en place. Wipe 3 large brinjals. Set a cast-iron grill or open flame and a steel kadhai — never aluminium.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Prick brinjals. Roast, turning, until the skin is charred and the flesh collapses, 15–20 minutes. Cool slightly. Peel. Mash with a fork — leave some texture.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Heat ghee in the kadhai. Bloom cumin and hing 20–30 seconds. Add ginger and green chilli. Add chopped tomato. Cook 6–8 minutes until jammy.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Add mashed baingan, salt and coriander. Cook 8–10 minutes, stirring, until the bharta looks dry-ish and smells smoky, not raw.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: no watery pool, smoky aroma, tomato melted. Taste salt and chilli.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Serve hot with roti. Hold covered. The dish improves after 10 minutes rest. Label nightshade if needed.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>kcal 4  ·  Protein 0 g  ·  Carbs 1 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="72" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>For Baingan bharta (no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="24">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1887,7 +2209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1899,7 +2221,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Punjabi kadhi pakora (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Punjabi kadhi pakora (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1909,7 +2231,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Side  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1929,44 +2251,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Prep 25 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -2132,35 +2454,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Fry pakora. Simmer kadhi. Add pakora. Temper.</t>
+          <t>Mise en place. Whisk yogurt and besan for the kadhi until lump-free. Mix a thicker besan batter for pakora with ajwain, chilli and optional spinach. Set a steel kadhai for frying and a heavy pot for simmering — never aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Heat frying oil to 175 C. Drop spoonfuls of pakora batter. Fry 4–5 minutes until gold and cooked through. Drain on a steel rack.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Thin the yogurt-besan mix with water. Pour into the pot. Add turmeric and salt. Bring to a gentle simmer, stirring so it does not split. Cook 20–25 minutes until the raw besan smell is gone and the kadhi coats a spoon.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Slip in pakora. Simmer 5 minutes so they soak but still hold a centre.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Tadka: ghee, cumin, methi seeds, dry chilli, hing — 20–30 seconds. Pour over. Cover 1 minute.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: kadhi silky, not chalky; pakora soft-centred. If it splits, whisk off the heat and do not boil hard.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Serve hot with rice. Hold on the lowest heat, stirred. Pakora continue to swell — add a splash of hot water if it thickens too far.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 208  ·  Protein 10 g  ·  Carbs 24 g  ·  Fat 7 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Punjabi kadhi pakora (no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2174,7 +2662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2186,7 +2674,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Makki di roti (maize, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Makki di roti (maize, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2196,7 +2684,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Bread  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2216,44 +2704,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2347,31 +2835,184 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Pat rotis. Cook on tawa. Ghee. Serve with saag.</t>
+          <t>Mise en place. Warm 3 cups makki atta with salt. Boil water. Set a cast-iron tawa — not aluminium.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="54" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Pour hot water into the atta gradually. Knead with wet hands to a soft, crack-free dough. Work in batches; maize dries fast. Keep unused dough covered with a damp cloth.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Pinch a ball. Flatten between oiled sheets or pat by hand to 15 cm, about 3 mm thick. Repair cracks with wet fingers.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cook on a medium tawa 1–2 minutes until the face dries. Flip. Cook the second side. Flip again and press gently until brown spots appear. Finish with ghee.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: no raw maize in the centre, edges set, spots brown not black. Stack in a cloth.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Serve hot with sarson da saag. Hold wrapped 20 minutes. Re-warm 20 seconds on the tawa if they stiffen.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>kcal 657  ·  Protein 16 g  ·  Carbs 133 g  ·  Fat 8 g  ·  Fibre 13 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="72" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>For Makki di roti (maize, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="24">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2385,7 +3026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2397,7 +3038,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Tandoori roti (atta, no garlic butter)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Tandoori roti (atta, no garlic butter)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2407,7 +3048,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Bread  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2427,44 +3068,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2558,31 +3199,184 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="54" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Roll. Stick in tandoor or cook on tawa. Ghee not garlic butter.</t>
+          <t>Mise en place. Mix 3 cups atta, salt and water to a soft dough. Rest 15 minutes. Set a clay tandoor or a cast-iron tawa — never garlic butter, never aluminium.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Divide into 8. Roll 3 mm thick. Lightly wet one face if using a tandoor so it sticks to the wall.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Bake in a hot tandoor 60–90 seconds until puffed with charred blisters. On a tawa: cook, then invert over the flame or press to puff.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Brush with plain ghee only.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: cooked through, light char, no wet dough. Serve immediately.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Hold in a cloth-lined steel box up to 15 minutes. Do not wrap in plastic.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>kcal 612  ·  Protein 22 g  ·  Carbs 130 g  ·  Fat 3 g  ·  Fibre 20 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="72" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>For Tandoori roti (atta, no garlic butter): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="24">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2596,7 +3390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2608,7 +3402,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Missi roti Punjabi (besan, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Missi roti Punjabi (besan, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2618,7 +3412,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Bread  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2638,44 +3432,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2787,32 +3581,172 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Knead. Cook on tawa.</t>
+          <t>Mise en place. Mix 2 cups atta, 1 cup besan, ajwain, chilli and salt. Add water to a firm dough. Rest 10 minutes. Set a cast-iron tawa.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Roll 3 mm thick. Dust with atta, not extra besan (besan burns).</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Cook on medium tawa until brown spots. Flip. Ghee on the cooked face. Flip again 20 seconds.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: no raw besan taste, spots even. Serve hot with dal or raita.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Hold wrapped 20 minutes. Refresh on the tawa.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>kcal 320  ·  Protein 14 g  ·  Carbs 61 g  ·  Fat 3 g  ·  Fibre 10 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="72" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>For Missi roti Punjabi (besan, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="24">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2826,7 +3760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2838,7 +3772,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pinni (atta-ghee-nuts)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pinni (atta-ghee-nuts)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2848,7 +3782,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Sweet  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2868,44 +3802,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 20 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -3035,33 +3969,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Roast atta in ghee. Mix sugar and nuts. Shape pinnis.</t>
+          <t>Mise en place. Weigh 2 cups atta, 1 cup ghee, 1 cup powdered sugar or jaggery, almonds and cardamom. Set a heavy steel kadhai — never aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Melt ghee. Add atta. Roast on low 18–22 minutes, stirring constantly, until the atta is biscuit-brown and smells like toasted wheat. Optional gond: fry in ghee first until it puffs, crush, add at the end.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Cool 8–10 minutes — sugar will melt if the mix is scorching hot. Stir in sugar, crushed cardamom and chopped almonds.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>While still warm, press into 40–45 g pinnis. Pack firmly so they do not crumble.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: roasted aroma, no raw atta, holds shape when cool.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cool fully. Store in a steel tin. Serve at room temperature. Label gluten, milk (ghee) and tree nuts.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 687  ·  Protein 7 g  ·  Carbs 81 g  ·  Fat 38 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Pinni (atta-ghee-nuts): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3075,7 +4162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3087,7 +4174,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Gajar ka halwa (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Gajar ka halwa (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3097,7 +4184,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Sweet  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3117,44 +4204,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>70 min</t>
+          <t>Prep 20 min · Cook 50 min</t>
         </is>
       </c>
     </row>
@@ -3302,34 +4389,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Cook carrot in milk till dry. Ghee, sugar, nuts.</t>
+          <t>Mise en place. Grate 1 kg red carrots. Measure 1 L milk, 3/4 cup sugar, 1/2 cup ghee. Set a heavy stainless steel kadhai — never aluminium (milk and carrot acid).</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cook carrot in the milk on medium, stirring, until the milk is absorbed and the mass is dry, 30–40 minutes.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Add ghee. Roast 8–10 minutes until the carrot shines and the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Add sugar. It will loosen. Cook until it leaves the sides of the pan, 8–12 minutes. Finish cardamom and nuts.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: glossy, spoon leaves a trail, no watery milk. Rest 5 minutes.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Serve hot or warm. Hold in a bain of hot water. Label milk and tree nuts.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 540  ·  Protein 10 g  ·  Carbs 66 g  ·  Fat 28 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Gajar ka halwa (no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3343,7 +4583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3355,7 +4595,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Atta gur pinni winter (jaggery)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Atta gur pinni winter (jaggery)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3365,7 +4605,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Sweet  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3385,44 +4625,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3552,33 +4792,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Roast atta. Mix jaggery. Shape.</t>
+          <t>Mise en place. Weigh 2 cups atta, 1 cup ghee, 1 cup grated jaggery, sesame and a pinch of dry ginger. Steel kadhai — never aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Roast atta in ghee on low 18–22 minutes to biscuit-brown.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Cool 5 minutes. Mix jaggery, sesame and ginger. Jaggery should melt from residual heat, not from a blast of flame (it burns).</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Shape pinnis while warm. Cool to set.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: holds shape, no raw atta, jaggery mixed through.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Store airtight. Serve at room temperature. Label gluten and sesame.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 685  ·  Protein 7 g  ·  Carbs 80 g  ·  Fat 38 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Atta gur pinni winter (jaggery): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3592,7 +4985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3604,7 +4997,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Phirni (Punjabi rice pudding)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Phirni (Punjabi rice pudding)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3614,7 +5007,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Dessert  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3634,44 +5027,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Prep 20 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -3783,32 +5176,185 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Cook rice paste in milk. Sugar, saffron. Pour in clay. Chill.</t>
+          <t>Mise en place. Soak 1/2 cup rice 30 minutes. Grind to a wet paste. Measure 1 L milk, sugar, saffron, cardamom. Heavy stainless steel milk pot and clay bowls — never aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Bring milk to a simmer. Stir in rice paste. Cook on low 20–25 minutes, stirring, until the phirni is thick and the rice is cooked, no grit.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Add sugar, saffron soaked in 1 tbsp warm milk, and cardamom. Cook 5 minutes more. It thickens further as it cools.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Pour into clay bowls. Cool. Chill at least 2 hours.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: sets to a soft quiver, grains fine, saffron aroma. No skin if you press cling on the surface.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Serve chilled. Hold refrigerated up to 24 hours. Label milk.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 246  ·  Protein 10 g  ·  Carbs 31 g  ·  Fat 9 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Phirni (Punjabi rice pudding): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="25">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4086,7 +5632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4098,7 +5644,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kheer (rice, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kheer (rice, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4108,7 +5654,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Dessert  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4128,44 +5674,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 10 min · Cook 45 min</t>
         </is>
       </c>
     </row>
@@ -4277,32 +5823,172 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Simmer till creamy.</t>
+          <t>Mise en place. Wash 1/2 cup basmati. Measure 1.5 L milk, sugar, cardamom, raisins, almonds. Heavy stainless steel milk pot — never aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Simmer rice in milk on low 35–45 minutes, stirring often so it does not catch. The kheer should look creamy and the rice should bloom.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Add sugar, cardamom, raisins and almonds. Cook 5 minutes. Sugar thins it; reduce 3 minutes more if needed.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: coats a spoon, rice tender, not porridge-glue. Rest 5 minutes.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Serve hot or chilled. Hold accordingly. Label milk and tree nuts.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>kcal 262  ·  Protein 13 g  ·  Carbs 22 g  ·  Fat 14 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="72" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>For Kheer (rice, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="24">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4316,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4328,7 +6014,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Lassi (sweet, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Lassi (sweet, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4338,7 +6024,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Dessert  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4358,44 +6044,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4525,33 +6211,173 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Blend in steel glass. Serve cold.</t>
+          <t>Mise en place. Chill 2 cups dahi, steel glasses and ice. Measure sugar, cardamom, optional malai. No onion, no savoury tadka.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Whisk or blend dahi with chilled water or milk, sugar and cardamom until frothy, 20–30 seconds. Do not over-blend or it goes thin and sour-tasting.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Taste sweetness. Adjust. Add ice to the glass, not the blender, if you want it to stay thick.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: pourable foam, no dahi lumps, cold through.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Serve immediately in a steel glass. Optional malai on top. Hold chilled up to 1 hour; stir before service. Label milk.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 78  ·  Protein 4 g  ·  Carbs 7 g  ·  Fat 4 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Lassi (sweet, no onion): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Serve in a steel or glass bowl. Stir at the pass so it is not split or settled. Service temperature: Chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="25">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4565,7 +6391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4577,7 +6403,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mooli salad (white radish, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mooli salad (white radish, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4587,7 +6413,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Salad  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4607,44 +6433,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4828,36 +6654,176 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Squeeze extra water. Toss.</t>
+          <t>Mise en place. Peel 2 white radishes and 1 carrot. Set a steel or glass bowl. No onion.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Grate. Squeeze firmly in a cloth to remove water or the salad weeps on the pass.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Toss with lemon, slit green chilli, salt, coriander and roasted cumin. Taste. It should be sharp and clean.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crisp, not wet; seasoning bright.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Serve cold at once. Hold 30 minutes covered and chilled. Drain if liquid collects. Label mustard if radish is an issue for the guest.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 12  ·  Protein 0 g  ·  Carbs 2 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Mooli salad (white radish, no onion): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4871,7 +6837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4883,7 +6849,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kheera raita (cucumber, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kheera raita (cucumber, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4893,7 +6859,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Salad  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4913,44 +6879,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5044,31 +7010,171 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Mix. Chill.</t>
+          <t>Mise en place. Whisk 2 cups dahi until smooth. Grate 1 cucumber. Set a steel or glass bowl. No onion.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Squeeze cucumber dry. Fold into dahi with roasted cumin, salt and chopped mint.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Chill 20 minutes so the flavours settle. Stir. Taste salt — cold dulls it slightly, so season a touch higher than you think.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: thick enough to mound, cucumber crisp, no water pooling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Serve cold. Hold chilled up to 2 hours. Stir at the pass. Label milk.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kcal 73  ·  Protein 4 g  ·  Carbs 6 g  ·  Fat 4 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B24" s="50" t="n"/>
+      <c r="C24" s="50" t="n"/>
+      <c r="D24" s="50" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>For Kheera raita (cucumber, no onion): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B29" s="52" t="n"/>
+      <c r="C29" s="52" t="n"/>
+      <c r="D29" s="52" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Serve in a steel or glass bowl. Stir at the pass so it is not split or settled. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="23">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5082,7 +7188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5094,7 +7200,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chana salad (boiled chickpea, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chana salad (boiled chickpea, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5104,7 +7210,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Salad  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5124,44 +7230,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Prep 15 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5255,31 +7361,171 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Toss. No onion.</t>
+          <t>Mise en place. Drain 2 cups boiled chickpeas well. Dice tomato and cucumber even and small. Steel or glass bowl. No onion.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Toss chickpeas with tomato, cucumber, lemon, chilli, cumin, salt and coriander. The lemon should coat, not puddle.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Rest 5 minutes. Toss again. Taste.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: chickpeas intact, vegetables crisp, seasoning even.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Serve cold. Hold 1 hour chilled. Do not add onion at the pass. Label legumes.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kcal 663  ·  Protein 0 g  ·  Carbs 0 g  ·  Fat 75 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B24" s="50" t="n"/>
+      <c r="C24" s="50" t="n"/>
+      <c r="D24" s="50" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>For Chana salad (boiled chickpea, no onion): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B29" s="52" t="n"/>
+      <c r="C29" s="52" t="n"/>
+      <c r="D29" s="52" t="n"/>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="23">
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -7303,7 +9549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7315,7 +9561,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Hara bhara kebab (no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Hara bhara kebab (no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7325,7 +9571,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Starter  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -7345,44 +9591,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 25 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -7620,39 +9866,257 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="54" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Mash. Shape. Shallow-fry on tawa.</t>
+          <t>Mise en place. Weigh every item for 4 portions. Set a cast-iron tawa (not aluminium) and a stainless steel pot of salted water. Check garam masala and chaat masala contain no onion or garlic powder.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Wash 2 cups spinach. Blanch in boiling water 45–60 seconds until wilted and bright. Shock in cold water. Squeeze very dry in a clean cloth — excess water makes kebabs collapse. Chop fine.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Boil 2 medium potatoes (about 250 g) until a knife slips through, 12–15 minutes. Drain. Steam-dry 2 minutes. Peel and mash while warm, leaving a little texture.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Boil or steam 1 cup green peas until tender, 4–5 minutes. Drain well. Lightly crush — do not puree to paste.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Dry-roast 2 tbsp (16 g) besan in a steel kadai on low heat 3–4 minutes until the raw smell goes and the flour turns biscuit-coloured. Cool.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="78" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>In a steel bowl combine spinach, potato, peas, roasted besan, 20 g crushed ginger, 2 finely chopped green chillies, 1/2 tsp garam masala, 1/2 tsp chaat masala and 1 tsp salt. Mix until the mass holds when pressed. If wet, add 1 tbsp more roasted besan; if dry and cracking, sprinkle 1 tsp water.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Rest 10 minutes. Divide into 12 portions of about 40 g. Shape into tikkis 1.5 cm thick with even edges so they brown evenly.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Chill 15 minutes uncovered on a steel tray — this sets the starch and stops them breaking on the tawa.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="66" customHeight="1">
+      <c r="A33" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>Heat the cast-iron tawa to medium. Add 1 tbsp ghee. When it shimmers, place kebabs without crowding. Cook 3–4 minutes until a deep green-brown crust forms. Flip once. Add remaining ghee as needed. Do not press hard or the filling squeezes out.</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust set, centre hot, no raw potato taste. Drain briefly on a steel rack.</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B35" s="48" t="inlineStr">
+        <is>
+          <t>Serve hot, 3 kebabs per portion, with imli chutney or plain dahi. Label allergens before the pass.</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="n"/>
+      <c r="D35" s="49" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="n"/>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>kcal 118  ·  Protein 3 g  ·  Carbs 9 g  ·  Fat 8 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+    </row>
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>Squeeze spinach bone-dry. Water is the usual reason kebabs break. Roasted besan is the binder — raw besan tastes pasty. Chill shaped kebabs at least 15 minutes before the tawa. Medium heat only; high heat colours the outside and leaves a wet centre. Make-ahead: shape and chill up to 6 hours. Fry to order. If grilling, make slightly thicker kebabs and oil the bars; chill 30 minutes first.</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="26" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B43" s="52" t="n"/>
+      <c r="C43" s="52" t="n"/>
+      <c r="D43" s="52" t="n"/>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B44" s="50" t="n"/>
+      <c r="C44" s="50" t="n"/>
+      <c r="D44" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="37">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -7666,7 +10130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7678,7 +10142,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Paneer tikka (dahi-ajwain, no garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Paneer tikka (dahi-ajwain, no garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7688,7 +10152,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Starter  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -7708,44 +10172,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 25 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -7911,35 +10375,227 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Marinate 1h. Skewer. Grill. Lemon.</t>
+          <t>Mise en place. Weigh 400 g paneer and 1 cup hung dahi. Set a cast-iron grill or steel oven tray — never aluminium foil. Confirm chilli powder and garam masala have no onion or garlic powder.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut paneer into even 2.5 cm cubes. Pat very dry. Cut capsicum and tomato into similar squares so they cook in the same time.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>In a steel bowl whisk hung dahi with 1 tsp ajwain, 1 tsp Kashmiri chilli, turmeric, garam masala, salt and crushed ginger to a thick marinade that coats a spoon. No garlic paste.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Fold paneer and vegetables through the marinade until every face is coated. Cover. Marinate 1 hour refrigerated (or 20 minutes at the pass if you are short of time).</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Thread onto steel skewers, alternating paneer and vegetable, leaving a little space between cubes so heat can circulate.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Heat the cast-iron grill to medium-high until a drop of water dances. Brush with ghee. Lay skewers. Do not crowd.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Grill 3–4 minutes per side until the dahi takes charred spots and the paneer is hot through. Turn with tongs. Brush once more with ghee.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: edges blistered, centre hot, dahi set not wet. Rest 1 minute so juices settle.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Finish with lemon juice at the pass. Serve 1 skewer per portion, hot. Hold no more than 10 minutes or the tikka steams and goes rubbery.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 311  ·  Protein 20 g  ·  Carbs 6 g  ·  Fat 23 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Paneer tikka (dahi-ajwain, no garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Pat paneer dry and do not boil it hard or it turns rubbery. Bring yogurt to a simmer gently and stir; a rolling boil can split it.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -7953,7 +10609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7965,7 +10621,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Samosa (aloo-peas, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Samosa (aloo-peas, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7975,7 +10631,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Starter  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -7995,44 +10651,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>65 min</t>
+          <t>Prep 40 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -8162,33 +10818,225 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Cook filling. Stuff cones. Fry.</t>
+          <t>Mise en place. Weigh 3 cups maida, ghee, ajwain and filling vegetables. Set a steel kadhai for frying — never aluminium. Oil should be 6–8 cm deep.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Rub ghee into maida with 1 tsp ajwain and salt until the mix looks like damp sand. Add water a spoon at a time to a firm dough. Rest covered 20 minutes.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Boil 4 potatoes until tender. Drain, steam-dry, peel and mash coarsely. Blanch 1 cup peas 3 minutes. Drain.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Heat ghee in a steel kadhai. Bloom cumin and a pinch of hing 20–30 seconds. Add potato, peas, chilli, coriander, amchur and salt. Cook 4–5 minutes until the filling is dry enough to hold a shape. Cool completely.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Divide dough into 10 balls. Roll each to a 15 cm oval. Cut in half. Form a cone, seal the straight edge with water, fill 2 tbsp cooled filling, seal the mouth firmly. No air pockets.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Heat oil to 170–175 C (a scrap of dough should rise in 8–10 seconds, not brown at once). Fry 4–5 samosas at a time.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Fry 8–10 minutes, turning, until blistered and deep gold. If they brown in under 4 minutes the oil is too hot and the pastry stays raw.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: pastry crisp, filling steaming hot, no greasy patches. Drain on a steel rack.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Serve hot with imli chutney. Hold 20 minutes in a low oven on a rack, not stacked. Label gluten and frying oil.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 701  ·  Protein 20 g  ·  Carbs 145 g  ·  Fat 2 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Samosa (aloo-peas, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="29">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8202,7 +11050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8214,7 +11062,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sarson da saag (no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sarson da saag (no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8224,7 +11072,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Main  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8244,44 +11092,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>80 min</t>
+          <t>Prep 20 min · Cook 60 min</t>
         </is>
       </c>
     </row>
@@ -8411,46 +11259,212 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Boil greens. Mash. Simmer with makki atta. Temper ghee, ginger, chilli, hing.</t>
+          <t>Mise en place. Pick through 1 kg mustard greens, 250 g spinach and optional bathua. Wash in several changes of water until grit is gone. Set a heavy stainless steel kadhai — never aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>Serve with makki roti and white butter.</t>
+          <t>Chop greens roughly. Slice ginger and green chilli. Keep 3 tbsp makki atta ready for thickening.</t>
         </is>
       </c>
       <c r="C20" s="31" t="n"/>
       <c r="D20" s="31" t="n"/>
     </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Put greens, ginger, chilli and salt in the kadhai with a splash of water. Cover. Cook on medium-low 35–45 minutes until the mustard is fully soft and the smell of raw saag is gone.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Mash with a wooden mathani or a potato masher to a coarse puree — not a blender slurry unless you prefer it smooth. Leave some fibre.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Sprinkle makki atta. Stir 8–10 minutes on low so the flour cooks out and the saag thickens to a slow ribbon. Add a little hot water if it catches.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>In a small steel tadka pan heat ghee. Bloom 1/2 tsp hing, remaining ginger and chilli 20–30 seconds. Pour over the saag. Stir.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: saag is silky, no raw maize-flour taste, mustard heat present but not bitter. Rest 3 minutes off the heat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Serve hot with makki di roti and a knob of white butter. Hold above 63 C. Do not store in aluminium. Reheat once only, loosening with hot water.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 72  ·  Protein 8 g  ·  Carbs 14 g  ·  Fat 1 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Wash greens until the water is clear; grit ruins the dish. For Sarson da saag (no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="28">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8464,7 +11478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8476,7 +11490,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Langar-style dal (urad-chana, no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Langar-style dal (urad-chana, no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8486,7 +11500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Main  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8506,44 +11520,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>90 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>105 min</t>
+          <t>Prep 15 min · Cook 90 min</t>
         </is>
       </c>
     </row>
@@ -8799,37 +11813,203 @@
       <c r="C25" s="46" t="n"/>
       <c r="D25" s="46" t="n"/>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="54" customHeight="1">
       <c r="A26" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B26" s="48" t="inlineStr">
         <is>
-          <t>Cook dals very soft. Temper. Mash slightly. Langar sattvic style.</t>
+          <t>Mise en place. Wash 1 cup sabut urad and 1/2 cup chana dal. Soak 30 minutes. Set a heavy stainless steel pot — langar dal wants a long, quiet simmer, never aluminium.</t>
         </is>
       </c>
       <c r="C26" s="49" t="n"/>
       <c r="D26" s="49" t="n"/>
     </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Drain. Cover with fresh water by 4 cm. Add turmeric, sliced ginger and salt. Bring to a boil. Skim foam.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Simmer 75–90 minutes, stirring every 10 minutes, until both dals collapse and the liquor is creamy. Add hot water as needed; the dal should look like a thick porridge, not soup.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Mash a third of the pot against the side so the gravy binds. Stir in chopped tomato. Cook 8 minutes until the tomato melts.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Tadka: heat ghee in a steel pan. Bloom cumin and hing 20–30 seconds, then chilli powder off the heat so it does not burn. Pour over the dal. Cover 2 minutes to trap the aroma.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: urad skins soft, chana creamy, no chalky centre. Salt should taste round, not sharp.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Serve hot in steel bowls, 1 ladle per portion, with roti or rice. Hold like langar: hot, loose, stirred. Cool quickly if storing. Reheat to a full simmer once.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>kcal 275  ·  Protein 14 g  ·  Carbs 37 g  ·  Fat 9 g  ·  Fibre 11 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>For Langar-style dal (urad-chana, no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="34">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
@@ -8846,7 +12026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8858,7 +12038,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chole (Amritsari-ish, no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chole (Amritsari-ish, no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8868,7 +12048,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Punjab kitchen  ·  Main  ·  Punjabi langar and home vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Punjab  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8888,44 +12068,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>70 min</t>
+          <t>Prep 20 min · Cook 50 min</t>
         </is>
       </c>
     </row>
@@ -9091,35 +12271,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Pressure-cook chana. Temper tomato-spice. Simmer thick. Anardana optional.</t>
+          <t>Mise en place. Soak 2 cups chickpeas overnight. Drain. Set a steel pressure cooker or heavy pot — never aluminium. Check chole masala for onion or garlic powder.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cook chickpeas with a teabag or a piece of amla, salt and water until very soft, 25–30 minutes under pressure or 60 minutes open. Drain, reserve 1 cup liquor. Discard the teabag.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Blend 2 tomatoes to a puree. Heat ghee in a steel kadhai. Bloom 1 tsp cumin and 1/2 tsp hing 20–30 seconds.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Add tomato, 2 tsp chole masala, chilli, amchur and salt. Cook 8–10 minutes until the fat separates and the puree looks jammy.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Add chickpeas and reserved liquor. Simmer 15–20 minutes, crushing a few chana against the pan so the gravy thickens. Optional: 1 tsp anardana.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: gravy coats a spoon, chickpeas creamy inside, colour deep brown-red. Rest 5 minutes.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Serve hot with bhatura or roti. Garnish coriander. Hold hot; the gravy skins if left uncovered. Label legumes.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 273  ·  Protein 14 g  ·  Carbs 46 g  ·  Fat 5 g  ·  Fibre 13 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Chole (Amritsari-ish, no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
